--- a/Les_IA_Avec_Cles_Gratuites.xlsx
+++ b/Les_IA_Avec_Cles_Gratuites.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github.com\Punkyherisson\LearningAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0C0F4B4-E9C9-400D-85E9-67746389BDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{65B34D75-8FD6-4AE3-A4AD-0B122888E9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{904080BF-B75A-42A7-A320-EFFC8565BFC8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{904080BF-B75A-42A7-A320-EFFC8565BFC8}"/>
   </bookViews>
   <sheets>
-    <sheet name="NomdelIA-URLAPI-Forces-Faib (2)" sheetId="3" r:id="rId1"/>
-    <sheet name="NomdelIA-URLAPI-Forces-Faibless" sheetId="1" r:id="rId2"/>
+    <sheet name="IA Standards" sheetId="3" r:id="rId1"/>
+    <sheet name="IA Specialisees" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">'NomdelIA-URLAPI-Forces-Faib (2)'!$A$1:$D$11</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">'IA Standards'!$A$1:$D$11</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -35,40 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
-  <si>
-    <t>Nom de lâ€™IA,"URL API","Forces","Faiblesses"</t>
-  </si>
-  <si>
-    <t>Google Gemini (AI Studio),"https://ai.google.dev/","ModÃ¨les multimodaux puissants, quotas gÃ©nÃ©reux, API simple","IntÃ©gration technique, rÃ©servÃ© aux devs avancÃ©s"</t>
-  </si>
-  <si>
-    <t>Hugging Face Inference,"https://huggingface.co/inference-api","Grande diversitÃ© de modÃ¨les, API flexible, communautÃ© active","Limites de taille de modÃ¨le, perf pouvant varier"</t>
-  </si>
-  <si>
-    <t>OpenRouter,"https://openrouter.ai/docs","AccÃ¨s universel Ã  de nombreux modÃ¨les, gestion centralisÃ©e des clÃ©s","Certains quotas gratuits flous selon modÃ¨le"</t>
-  </si>
-  <si>
-    <t>Groq,"https://console.groq.com/","Excellente rapiditÃ©, accÃ¨s Ã  des modÃ¨les open source optimisÃ©s","FonctionnalitÃ©s avancÃ©es limitÃ©es, modÃ¨les spÃ©cifiques"</t>
-  </si>
-  <si>
-    <t>Cohere,"https://dashboard.cohere.com/api-keys","ModÃ¨les texte fiables, documentation claire","Quotas gratuits mensuels faibles pour de gros besoins"</t>
-  </si>
-  <si>
-    <t>Clarifai,"https://portal.clarifai.com/signup","SpÃ©cialisÃ©e image/vidÃ©o, outils annotatifs complets","1 000 requÃªtes gratuites/mois, API complexe"</t>
-  </si>
-  <si>
-    <t>Mistral AI,"https://docs.mistral.ai/","ModÃ¨les franÃ§ais/francophones solides, API gratuite (usage limitÃ©)","Moins robuste que Gemini/OpenAI selon tÃ¢ches, doc perfectible"</t>
-  </si>
-  <si>
-    <t>DeepSeek,"https://platform.deepseek.com/docs","Bon rapport rapiditÃ©/prix, accÃ¨s API direct","Documentation technique, idÃ©al via OpenRouter"</t>
-  </si>
-  <si>
-    <t>Anthropic Claude (mini),"https://docs.anthropic.com/claude/docs/getting-started","Bon pour le dialogue, sÃ©curitÃ© conversation IA","Version gratuite limitÃ©e, accÃ¨s via agrÃ©gateur (OpenRouter)"</t>
-  </si>
-  <si>
-    <t>Meta Llama,"https://llama.meta.com/get-started/","Raisonnement avancÃ©, open source, accÃ¨s via HuggingFace/OpenRouter","Pas d'API directe Meta, accÃ¨s indirect avec quota"</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="93">
   <si>
     <t>Nom de l’IA</t>
   </si>
@@ -200,6 +167,153 @@
   </si>
   <si>
     <t>Pas d'API directe Meta, accès indirect avec quota</t>
+  </si>
+  <si>
+    <t>Spécialisation</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Speechify</t>
+  </si>
+  <si>
+    <t>OCR + Synthèse vocale</t>
+  </si>
+  <si>
+    <t>Conversion facile d’images en textes lus</t>
+  </si>
+  <si>
+    <t>Limites en gratuit, voix parfois robotiques</t>
+  </si>
+  <si>
+    <t>https://speechify.com/fr</t>
+  </si>
+  <si>
+    <t>Reconnaissance image</t>
+  </si>
+  <si>
+    <t>Analyse et classification d’images/vidéo</t>
+  </si>
+  <si>
+    <t>1000 requêtes gratuites/mois max</t>
+  </si>
+  <si>
+    <t>EaseMate AI</t>
+  </si>
+  <si>
+    <t>OCR image en texte</t>
+  </si>
+  <si>
+    <t>Simple, multiple formats supportés</t>
+  </si>
+  <si>
+    <t>Fonctionnalités basiques</t>
+  </si>
+  <si>
+    <t>https://www.easemate.ai/fr/ai-image-to-text-converter</t>
+  </si>
+  <si>
+    <t>DALL-E (OpenAI)</t>
+  </si>
+  <si>
+    <t>Génération d’images</t>
+  </si>
+  <si>
+    <t>Création d'images de haute qualité</t>
+  </si>
+  <si>
+    <t>Usage gratuit limité</t>
+  </si>
+  <si>
+    <t>https://openai.com/dall-e</t>
+  </si>
+  <si>
+    <t>ElevenLabs</t>
+  </si>
+  <si>
+    <t>Synthèse vocale</t>
+  </si>
+  <si>
+    <t>Voix naturelles et personnalisables</t>
+  </si>
+  <si>
+    <t>Limite sur durée gratuite</t>
+  </si>
+  <si>
+    <t>https://elevenlabs.io</t>
+  </si>
+  <si>
+    <t>Notion AI</t>
+  </si>
+  <si>
+    <t>Productivité textuelle</t>
+  </si>
+  <si>
+    <t>Intégration dans Notion, polyvalent</t>
+  </si>
+  <si>
+    <t>Limitations dans la version gratuite</t>
+  </si>
+  <si>
+    <t>https://www.notion.so/product/ai</t>
+  </si>
+  <si>
+    <t>Google Cloud Vision</t>
+  </si>
+  <si>
+    <t>Vision par ordinateur</t>
+  </si>
+  <si>
+    <t>Reconnaissance d’objets, étiquetage</t>
+  </si>
+  <si>
+    <t>Coût au-delà des paliers gratuits</t>
+  </si>
+  <si>
+    <t>https://cloud.google.com/vision</t>
+  </si>
+  <si>
+    <t>Google Speech-to-Text</t>
+  </si>
+  <si>
+    <t>Transcription audio</t>
+  </si>
+  <si>
+    <t>Précision élevée, multi-langues</t>
+  </si>
+  <si>
+    <t>Coût après quotas gratuits</t>
+  </si>
+  <si>
+    <t>https://cloud.google.com/speech-to-text</t>
+  </si>
+  <si>
+    <t>Rytr</t>
+  </si>
+  <si>
+    <t>Génération texte</t>
+  </si>
+  <si>
+    <t>Génération rapide de contenu marketing</t>
+  </si>
+  <si>
+    <t>Fonctionnalités limitées en version gratuite</t>
+  </si>
+  <si>
+    <t>https://rytr.me</t>
+  </si>
+  <si>
+    <t>Midjourney</t>
+  </si>
+  <si>
+    <t>Esthétique artistique, AI créative</t>
+  </si>
+  <si>
+    <t>Modèle d’abonnement, gratuit limité</t>
+  </si>
+  <si>
+    <t>https://www.midjourney.com</t>
   </si>
 </sst>
 </file>
@@ -780,6 +894,20 @@
     <tableColumn id="4" xr3:uid="{8DD85EFB-AB4F-45F4-81B3-D3CD1EA37C2F}" uniqueName="4" name="Faiblesses" queryTableFieldId="4" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E3B0BE4D-F0D3-43E5-BBC9-0A75B63C673E}" name="Table3" displayName="Table3" ref="A1:E11" totalsRowShown="0">
+  <autoFilter ref="A1:E11" xr:uid="{E3B0BE4D-F0D3-43E5-BBC9-0A75B63C673E}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{71CE34D8-3041-4738-8807-E6CCF33ED0F8}" name="Nom de l’IA"/>
+    <tableColumn id="2" xr3:uid="{D49C27BA-68C5-4511-9B00-26AD662AF386}" name="Spécialisation"/>
+    <tableColumn id="3" xr3:uid="{B513899F-6472-4A5C-9488-D5632B37A668}" name="Forces"/>
+    <tableColumn id="4" xr3:uid="{734DF2AE-162D-41E4-AFAE-59B77FFD574E}" name="Faiblesses"/>
+    <tableColumn id="5" xr3:uid="{42B16B10-B0E4-4804-AC51-6C249E9B903C}" name="URL"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1111,156 +1239,156 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1273,66 +1401,208 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6314274-21F3-4675-9E05-88693FC4B656}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" customWidth="1"/>
+    <col min="5" max="5" width="46.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+      <c r="B5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="B9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>89</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
